--- a/dataset2.xlsx
+++ b/dataset2.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://technip-my.sharepoint.com/personal/rahul_agrawal4_ten_com/Documents/Attachments/FPSO MACI files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{24F324EF-5242-410A-9C40-D358DF986B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C9A4148-6D35-4E7B-AA58-78C00512BA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11790" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{CA8FCB40-F318-4175-8708-AAF348325576}"/>
+    <workbookView xWindow="11790" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{DA2644FE-99A7-474E-A513-FB4199514A10}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,42 +39,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="130">
   <si>
     <t>OED ID</t>
   </si>
   <si>
-    <t>OFFPEX  ID</t>
-  </si>
-  <si>
-    <t>Field</t>
+    <t>Platform Name</t>
+  </si>
+  <si>
+    <t>Facility Type</t>
+  </si>
+  <si>
+    <t>Facility Status</t>
+  </si>
+  <si>
+    <t>product</t>
+  </si>
+  <si>
+    <t>Location</t>
   </si>
   <si>
     <t>Country</t>
   </si>
   <si>
-    <t>WM Region</t>
-  </si>
-  <si>
-    <t>Label</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>--- HISTORICAL ---</t>
-  </si>
-  <si>
-    <t>Old Status</t>
-  </si>
-  <si>
-    <t>WoodMack FID date</t>
-  </si>
-  <si>
-    <t>WM Award date</t>
-  </si>
-  <si>
-    <t>WM estimated Installation date</t>
+    <t>WMSuperRegion</t>
+  </si>
+  <si>
+    <t>Hull award year</t>
+  </si>
+  <si>
+    <t>Installation year</t>
+  </si>
+  <si>
+    <t>New Build Hull</t>
+  </si>
+  <si>
+    <t>OWNED/LEASED</t>
+  </si>
+  <si>
+    <t>Operator Group</t>
+  </si>
+  <si>
+    <t>TAM</t>
   </si>
   <si>
     <t>SAM</t>
@@ -83,100 +89,346 @@
     <t>SOM</t>
   </si>
   <si>
-    <t>--- CURRENT ---</t>
-  </si>
-  <si>
-    <t>Facility Status</t>
-  </si>
-  <si>
-    <t>Operator</t>
-  </si>
-  <si>
-    <t>Platform Owner</t>
-  </si>
-  <si>
-    <t>Contract Type</t>
-  </si>
-  <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>Oil Capacity</t>
-  </si>
-  <si>
-    <t>Gas Capacity</t>
-  </si>
-  <si>
-    <t>Water Depth</t>
-  </si>
-  <si>
-    <t>is SAM?</t>
-  </si>
-  <si>
-    <t>is SOM?</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Budiao (Ex Moita Bonita) (BM-SEAL-10) SEAP-II</t>
+    <t>EPCI Floater contractor</t>
+  </si>
+  <si>
+    <t>EPCI FLOATER-TOPSIDE Contractor</t>
+  </si>
+  <si>
+    <t>Platform Green/Brownfield</t>
+  </si>
+  <si>
+    <t>Water Depth Group (M)</t>
+  </si>
+  <si>
+    <t>Topside Weight (Tonnes)</t>
+  </si>
+  <si>
+    <t>Topside Configuration</t>
+  </si>
+  <si>
+    <t>EPCI Capex</t>
+  </si>
+  <si>
+    <t>Max Oil Production Rate (bbl/d)</t>
+  </si>
+  <si>
+    <t>Max Gas Production Rate (mmcfd)</t>
+  </si>
+  <si>
+    <t>FPSO</t>
+  </si>
+  <si>
+    <t>Conceptual</t>
+  </si>
+  <si>
+    <t>Oil/Gas</t>
+  </si>
+  <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>Refurbishment</t>
+  </si>
+  <si>
+    <t>Lease</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1000-1499</t>
+  </si>
+  <si>
+    <t>Acc/Prod/Sep/Sto/Fl</t>
+  </si>
+  <si>
+    <t>FEED</t>
+  </si>
+  <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>OpOwn</t>
+  </si>
+  <si>
+    <t>100-499</t>
+  </si>
+  <si>
+    <t>Acc/Prod/Sep/Inj/Sto/Fl</t>
+  </si>
+  <si>
+    <t>Nam Du FPSO</t>
+  </si>
+  <si>
+    <t>Gas/Condensate</t>
+  </si>
+  <si>
+    <t>7 26 37.32N 103 54 32.40E</t>
+  </si>
+  <si>
+    <t>Vietnam</t>
+  </si>
+  <si>
+    <t>Conversion</t>
+  </si>
+  <si>
+    <t>Jadestone</t>
+  </si>
+  <si>
+    <t>Greenfield</t>
+  </si>
+  <si>
+    <t>0-99</t>
+  </si>
+  <si>
+    <t>Tangkulo FPSO</t>
+  </si>
+  <si>
+    <t>Bidding</t>
+  </si>
+  <si>
+    <t>5 49 56.66N 96 53 7.49E</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>Mubadala</t>
+  </si>
+  <si>
+    <t>Venus Phase 1 FPSO (Namibia)</t>
+  </si>
+  <si>
+    <t>29 31 3.70S 13 12 55.65E</t>
+  </si>
+  <si>
+    <t>Namibia</t>
+  </si>
+  <si>
+    <t>New Build</t>
+  </si>
+  <si>
+    <t>TotalEnergies</t>
+  </si>
+  <si>
+    <t>Shanghai Waigaoqiao Shipbuilding SWS</t>
+  </si>
+  <si>
+    <t>&gt;1499</t>
+  </si>
+  <si>
+    <t>Guyana</t>
+  </si>
+  <si>
+    <t>Latin America and the Caribbean</t>
+  </si>
+  <si>
+    <t>ExxonMobil</t>
+  </si>
+  <si>
+    <t>SBM Offshore</t>
+  </si>
+  <si>
+    <t>Oil/Gas/Condensate</t>
+  </si>
+  <si>
+    <t>North America</t>
+  </si>
+  <si>
+    <t>500-999</t>
   </si>
   <si>
     <t>Brazil</t>
   </si>
   <si>
-    <t>Latin America and the Caribbean</t>
-  </si>
-  <si>
-    <t>Budiao FPSO (Sergipe-Alagoas FPSO-2) (SEAP-2)</t>
-  </si>
-  <si>
-    <t>11 15S 36 20W</t>
-  </si>
-  <si>
-    <t>Bidding</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>Awarded</t>
-  </si>
-  <si>
-    <t>Under Development</t>
-  </si>
-  <si>
-    <t>Cavala (Ex Farfan) (BM-SEAL-11) SEAP-I</t>
-  </si>
-  <si>
-    <t>FPSO P-81 (Sergipe-Alagoas FPSO-1) (SEAP-1)</t>
-  </si>
-  <si>
-    <t>11 02S 36 11W</t>
-  </si>
-  <si>
-    <t>Keratau (CA-2) (Kelidang Cluster)</t>
-  </si>
-  <si>
-    <t>Brunei</t>
-  </si>
-  <si>
-    <t>Asia</t>
-  </si>
-  <si>
-    <t>Keratau FPSO (Kelidang Cluster)</t>
-  </si>
-  <si>
-    <t>05 33N 113 44E</t>
-  </si>
-  <si>
-    <t>Conceptual</t>
-  </si>
-  <si>
-    <t>Under Conversion</t>
+    <t>Petrobras</t>
+  </si>
+  <si>
+    <t>Brownfield</t>
+  </si>
+  <si>
+    <t>Nigeria</t>
+  </si>
+  <si>
+    <t>Abadi FPSO</t>
+  </si>
+  <si>
+    <t>9 11 24.00S 130 20 24.00E</t>
+  </si>
+  <si>
+    <t>Inpex</t>
+  </si>
+  <si>
+    <t>Albacora P-88 FPSO (Revitalisation)</t>
+  </si>
+  <si>
+    <t>22 7 42.60S 39 58 7.20W</t>
+  </si>
+  <si>
+    <t>Bay du Nord FPSO</t>
+  </si>
+  <si>
+    <t>47 57 49.65N 46 23 0.89W</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Equinor</t>
+  </si>
+  <si>
+    <t>Bonga Southwest - Aparo FPSO</t>
+  </si>
+  <si>
+    <t>3 52 54.41N 6 20 8.86E</t>
+  </si>
+  <si>
+    <t>Shell</t>
+  </si>
+  <si>
+    <t>Buzios (FPSO-12)</t>
+  </si>
+  <si>
+    <t>24 41 60.00S 42 27 0.00W</t>
+  </si>
+  <si>
+    <t>Fangtooth FPSO (FPSO-9)</t>
+  </si>
+  <si>
+    <t>8 11 22.01N 57 4 33.37W</t>
+  </si>
+  <si>
+    <t>Neon FPSO (Piranema Spirit FPSO)</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>26 0 0.00S 46 0 0.00W</t>
+  </si>
+  <si>
+    <t>Karoon</t>
+  </si>
+  <si>
+    <t>Calliance/Brecknock FPSO (Browse Basin)</t>
+  </si>
+  <si>
+    <t>14 32 34.95S 121 37 21.01E</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>Woodside</t>
+  </si>
+  <si>
+    <t>Torosa FPSO (Browse Basin)</t>
+  </si>
+  <si>
+    <t>13 58 16.44S 122 1 28.55E</t>
+  </si>
+  <si>
+    <t>Kalimba FPSO (Southeast Hub 15/06)</t>
+  </si>
+  <si>
+    <t>6 31 35.00S 11 29 19.00E</t>
+  </si>
+  <si>
+    <t>Angola</t>
+  </si>
+  <si>
+    <t>Azule Energy</t>
+  </si>
+  <si>
+    <t>Kuda/Singa Laut FPSO</t>
+  </si>
+  <si>
+    <t>6 39 0.00N 108 39 0.00E</t>
+  </si>
+  <si>
+    <t>Prime Group</t>
+  </si>
+  <si>
+    <t>Marlim Sul P-86 FPSO 2</t>
+  </si>
+  <si>
+    <t>22 36 0.00S 40 2 60.00W</t>
+  </si>
+  <si>
+    <t>Wisting FPSO</t>
+  </si>
+  <si>
+    <t>73 27 36.00N 24 23 60.00E</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>Acc/Prod/Sep/Inj/Sto/Fl/CCS</t>
+  </si>
+  <si>
+    <t>Yarrow FPSO (FPSO-10)</t>
+  </si>
+  <si>
+    <t>7 43 17.40N 56 44 47.04W</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>Bosi FPSO</t>
+  </si>
+  <si>
+    <t>5 20 60.00N 4 10 0.00E</t>
+  </si>
+  <si>
+    <t>Barracuda FPSO 2</t>
+  </si>
+  <si>
+    <t>22 34 59.88S 40 11 58.80W</t>
+  </si>
+  <si>
+    <t>Ranger FPSO (FPSO-11)</t>
+  </si>
+  <si>
+    <t>8 54 18.00N 57 18 22.80W</t>
+  </si>
+  <si>
+    <t>Dorado FPSO</t>
+  </si>
+  <si>
+    <t>19 0 0.00S 118 45 0.00E</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Acc/Prod/Sep/Sto/Comp/Fl</t>
+  </si>
+  <si>
+    <t>Pilot FPSO</t>
+  </si>
+  <si>
+    <t>57 4 12.00N 0 15 0.00E</t>
+  </si>
+  <si>
+    <t>Ping (Dagang Nexchange)</t>
+  </si>
+  <si>
+    <t>Venus Phase 2 FPSO (Namibia)</t>
   </si>
 </sst>
 </file>
@@ -192,14 +444,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -208,12 +461,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -221,17 +492,71 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,259 +890,1859 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50095F9C-2154-4489-B957-D8792116B0EF}">
-  <dimension ref="A1:Z4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42ADF700-7199-4285-ABE4-05E0E6BA4FBB}">
+  <dimension ref="B2:Z25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.90625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="2" spans="2:26" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+    </row>
+    <row r="3" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B3" s="1">
+        <v>220529</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
-        <v>220557</v>
-      </c>
-      <c r="B2" s="2">
-        <v>401150</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="2">
-        <v>2026</v>
-      </c>
-      <c r="K2" s="2">
-        <v>2026</v>
-      </c>
-      <c r="L2" s="2">
-        <v>2030</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="2"/>
-      <c r="P2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" s="2">
-        <v>2026</v>
-      </c>
-      <c r="S2" s="2">
-        <v>2026</v>
-      </c>
-      <c r="T2" s="2">
-        <v>2031</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
-        <v>218930</v>
-      </c>
-      <c r="B3" s="2">
-        <v>351368</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="F3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="J3" s="2">
         <v>2026</v>
       </c>
       <c r="K3" s="2">
+        <v>2029</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V3" s="2">
+        <v>5000</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X3" s="2">
+        <v>388.00799815177919</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B4" s="3">
+        <v>222050</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="4">
         <v>2026</v>
       </c>
-      <c r="L3" s="2">
+      <c r="K4" s="4">
+        <v>2029</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="V4" s="4">
+        <v>8000</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="X4" s="4">
+        <v>450.66872197151184</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>6000</v>
+      </c>
+      <c r="Z4" s="6">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B5" s="1">
+        <v>221096</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="2">
+        <v>2026</v>
+      </c>
+      <c r="K5" s="2">
+        <v>2031</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="V5" s="2">
+        <v>30000</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X5" s="2">
+        <v>1596.6124932861328</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>160000</v>
+      </c>
+      <c r="Z5" s="5">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="6" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B6" s="3">
+        <v>219079</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="4">
+        <v>2027</v>
+      </c>
+      <c r="K6" s="4">
+        <v>2032</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="V6" s="4">
+        <v>40000</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="X6" s="4">
+        <v>2550</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B7" s="1">
+        <v>221854</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J7" s="2">
+        <v>2027</v>
+      </c>
+      <c r="K7" s="2">
+        <v>2032</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V7" s="2">
+        <v>6000</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X7" s="2">
+        <v>225.33436098575592</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>120000</v>
+      </c>
+      <c r="Z7" s="5">
+        <v>211.89</v>
+      </c>
+    </row>
+    <row r="8" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B8" s="3">
+        <v>219131</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="4">
+        <v>2027</v>
+      </c>
+      <c r="K8" s="4">
+        <v>2031</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="V8" s="4">
+        <v>17244</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X8" s="4">
+        <v>2679.5399221801758</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>160000</v>
+      </c>
+      <c r="Z8" s="6">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B9" s="1">
+        <v>213106</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="2">
+        <v>2027</v>
+      </c>
+      <c r="K9" s="2">
+        <v>2031</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="V9" s="2">
+        <v>20000</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X9" s="2">
+        <v>3981.0600350189211</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>150000</v>
+      </c>
+      <c r="Z9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B10" s="3">
+        <v>221218</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" s="4">
+        <v>2027</v>
+      </c>
+      <c r="K10" s="4">
+        <v>2032</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="V10" s="4">
+        <v>47000</v>
+      </c>
+      <c r="W10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X10" s="4">
+        <v>2501.3596293640135</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>180000</v>
+      </c>
+      <c r="Z10" s="6">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B11" s="1">
+        <v>221262</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="2">
+        <v>2027</v>
+      </c>
+      <c r="K11" s="2">
         <v>2030</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="L11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="O11" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="V11" s="2">
+        <v>30000</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X11" s="2">
+        <v>1596.6124932861328</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B12" s="3">
+        <v>220649</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J12" s="4">
+        <v>2027</v>
+      </c>
+      <c r="K12" s="4">
+        <v>2029</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q12" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="3" t="s">
+      <c r="R12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="V12" s="4">
+        <v>8000</v>
+      </c>
+      <c r="W12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="X12" s="4">
+        <v>300.44580508232116</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>25000</v>
+      </c>
+      <c r="Z12" s="6">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B13" s="1">
+        <v>220174</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J13" s="2">
+        <v>2028</v>
+      </c>
+      <c r="K13" s="2">
+        <v>2032</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="O13" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V13" s="2">
+        <v>63000</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X13" s="2">
+        <v>4079.9998443603517</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B14" s="3">
+        <v>220175</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J14" s="4">
+        <v>2028</v>
+      </c>
+      <c r="K14" s="4">
+        <v>2032</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="V14" s="4">
+        <v>63000</v>
+      </c>
+      <c r="W14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="X14" s="4">
+        <v>4079.9998443603517</v>
+      </c>
+      <c r="Y14" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="6">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="15" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B15" s="1">
+        <v>220482</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="2">
+        <v>2028</v>
+      </c>
+      <c r="K15" s="2">
+        <v>2030</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V15" s="2">
+        <v>17000</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X15" s="2">
+        <v>796.82399883270261</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>60000</v>
+      </c>
+      <c r="Z15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B16" s="3">
+        <v>219420</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="4">
+        <v>2028</v>
+      </c>
+      <c r="K16" s="4">
+        <v>2030</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="U16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="V16" s="4">
+        <v>5000</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X16" s="4">
+        <v>187.77862446784974</v>
+      </c>
+      <c r="Y16" s="4">
+        <v>20000</v>
+      </c>
+      <c r="Z16" s="6">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B17" s="1">
+        <v>221186</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J17" s="2">
+        <v>2028</v>
+      </c>
+      <c r="K17" s="2">
+        <v>2032</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="U17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="V17" s="2">
+        <v>20000</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X17" s="2">
+        <v>1064.4084264564515</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>140000</v>
+      </c>
+      <c r="Z17" s="5">
+        <v>211.88</v>
+      </c>
+    </row>
+    <row r="18" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B18" s="3">
+        <v>221367</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J18" s="4">
+        <v>2028</v>
+      </c>
+      <c r="K18" s="4">
+        <v>2032</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="O18" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P18" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q18" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="R18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="U18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="V18" s="4">
+        <v>18000</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="X18" s="4">
+        <v>638.64500976562499</v>
+      </c>
+      <c r="Y18" s="4">
+        <v>220000</v>
+      </c>
+      <c r="Z18" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B19" s="1">
+        <v>220392</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J19" s="2">
+        <v>2028</v>
+      </c>
+      <c r="K19" s="2">
+        <v>2031</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="O19" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="V19" s="2">
+        <v>30000</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X19" s="2">
+        <v>1755.4199280166627</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>220000</v>
+      </c>
+      <c r="Z19" s="5">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B20" s="3">
+        <v>212021</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="4">
+        <v>2029</v>
+      </c>
+      <c r="K20" s="4">
+        <v>2032</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O20" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="V20" s="4">
+        <v>20000</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X20" s="4">
+        <v>1047.6565964698791</v>
+      </c>
+      <c r="Y20" s="4">
+        <v>140000</v>
+      </c>
+      <c r="Z20" s="6">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="21" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B21" s="1">
+        <v>221185</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J21" s="2">
+        <v>2029</v>
+      </c>
+      <c r="K21" s="2">
+        <v>2031</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="O21" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P21" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q21" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="V21" s="2">
+        <v>20000</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X21" s="2">
+        <v>976.44885423660276</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>100000</v>
+      </c>
+      <c r="Z21" s="5">
+        <v>211.8</v>
+      </c>
+    </row>
+    <row r="22" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B22" s="3">
+        <v>220240</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J22" s="4">
+        <v>2029</v>
+      </c>
+      <c r="K22" s="4">
+        <v>2033</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O22" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="V22" s="4">
+        <v>30000</v>
+      </c>
+      <c r="W22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X22" s="4">
+        <v>1733.9999513626099</v>
+      </c>
+      <c r="Y22" s="4">
+        <v>50000</v>
+      </c>
+      <c r="Z22" s="6">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="23" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B23" s="1">
+        <v>219485</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J23" s="2">
+        <v>2030</v>
+      </c>
+      <c r="K23" s="2">
+        <v>2032</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="O23" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V23" s="2">
+        <v>8000</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="X23" s="2">
+        <v>941.459995136261</v>
+      </c>
+      <c r="Y23" s="2">
+        <v>100000</v>
+      </c>
+      <c r="Z23" s="5">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B24" s="3">
+        <v>212001</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J24" s="4">
+        <v>2030</v>
+      </c>
+      <c r="K24" s="4">
+        <v>2033</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="O24" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P24" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q24" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="S24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T24" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="V24" s="4">
+        <v>5000</v>
+      </c>
+      <c r="W24" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="R3" s="2">
-        <v>2026</v>
-      </c>
-      <c r="S3" s="2">
-        <v>2026</v>
-      </c>
-      <c r="T3" s="2">
-        <v>2031</v>
+      <c r="X24" s="4">
+        <v>393.26726079940795</v>
+      </c>
+      <c r="Y24" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <v>221234</v>
-      </c>
-      <c r="B4" s="2">
-        <v>415137</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="2" t="s">
+    <row r="25" spans="2:26" x14ac:dyDescent="0.35">
+      <c r="B25" s="1">
+        <v>221740</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J25" s="2">
+        <v>2030</v>
+      </c>
+      <c r="K25" s="2">
+        <v>2035</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O25" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="V25" s="2">
+        <v>30000</v>
+      </c>
+      <c r="W25" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="2">
-        <v>2025</v>
-      </c>
-      <c r="K4" s="2">
-        <v>2025</v>
-      </c>
-      <c r="L4" s="2">
-        <v>2027</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R4" s="2">
-        <v>2025</v>
-      </c>
-      <c r="S4" s="2">
-        <v>2025</v>
-      </c>
-      <c r="T4" s="2">
-        <v>2029</v>
+      <c r="X25" s="2">
+        <v>1596.6124932861328</v>
+      </c>
+      <c r="Y25" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -830,6 +2755,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{b29603fb-7fab-4bf6-8ed3-004985bb9d91}" enabled="1" method="Standard" siteId="{9179d01a-e94c-4488-b5f0-4554bc474f8c}" contentBits="1" removed="0"/>
+  <clbl:label id="{b29603fb-7fab-4bf6-8ed3-004985bb9d91}" enabled="1" method="Standard" siteId="{9179d01a-e94c-4488-b5f0-4554bc474f8c}" removed="0"/>
 </clbl:labelList>
 </file>